--- a/examples/autos/Plantilla Comparativa Autos - Zurich.xlsx
+++ b/examples/autos/Plantilla Comparativa Autos - Zurich.xlsx
@@ -5592,9 +5592,8 @@
       <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Asistencia en Viaje 24h Esencial Green:
--Asistencia en carretera por descarga de la batería
--Remolque sin límite de Km hasta un punto de
-recarga</t>
+• Asistencia en carretera por descarga de la batería
+• Remolque sin límite de Km hasta un punto de recarga</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5667,10 +5666,10 @@
 • Envío de llaves de repuesto
 • Anticipo de fianza judicial en extranjero.
 • Gastos de defensa legal en extranjero.
-Green: -Asistencia para el uso de puntos de recarga
--Configuración de dispositivos del vehículo
--Asesoramiento sobre el cuadro de mandos
-(mensajes de error)</t>
+GREEN:
+• Asistencia para el uso de puntos de recarga
+• Configuración de dispositivos del vehículo
+• Asesoramiento sobre el cuadro de mandos (mensajes de error)</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -5743,8 +5742,8 @@
 • Envío de llaves de repuesto
 • Anticipo de fianza judicial en extranjero.
 • Gastos de defensa legal en extranjero.
-Green: -Vehículo de sustitución eco en caso de
-siniestro.</t>
+GREEN:
+• Vehículo de sustitución eco en caso de siniestro.</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -6073,7 +6072,7 @@
       <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Vehículo sustitución : contratado
--En caso de accidente y robo hasta 14 días desde el momento del siniestro cuando la reparación supere las 8horas según peritaje y baremo de la compañía.</t>
+• En caso de accidente y robo hasta 14 días desde el momento del siniestro cuando la reparación supere las 8horas según peritaje y baremo de la compañía.</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
